--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\Glow_pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0762FC-358F-4A92-A147-39540EF961F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE95E6AF-1EEC-4260-B83D-A0C2C2A5DC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{42CED176-6331-4827-B98C-A46AFC054923}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{42CED176-6331-4827-B98C-A46AFC054923}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_aplicativo_Glow" sheetId="1" r:id="rId1"/>
     <sheet name="FN1" sheetId="2" r:id="rId2"/>
     <sheet name="FN2" sheetId="4" r:id="rId3"/>
+    <sheet name="FN3" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="175">
   <si>
     <t>cliente</t>
   </si>
@@ -476,13 +477,100 @@
   </si>
   <si>
     <t>id_reserva</t>
+  </si>
+  <si>
+    <t>id_cliente</t>
+  </si>
+  <si>
+    <t>id_trabajador</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>T003</t>
+  </si>
+  <si>
+    <t>nom_clie</t>
+  </si>
+  <si>
+    <t>ape_cliente</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>D001</t>
+  </si>
+  <si>
+    <t>D002</t>
+  </si>
+  <si>
+    <t>id_tdoc</t>
+  </si>
+  <si>
+    <t>tdoc</t>
+  </si>
+  <si>
+    <t>Tipodocumento</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Cl001</t>
+  </si>
+  <si>
+    <t>Cl002</t>
+  </si>
+  <si>
+    <t>Cl003</t>
+  </si>
+  <si>
+    <t>Cl004</t>
+  </si>
+  <si>
+    <t>Cl005</t>
+  </si>
+  <si>
+    <t>Cl006</t>
+  </si>
+  <si>
+    <t>id_trab</t>
+  </si>
+  <si>
+    <t>Reserva</t>
+  </si>
+  <si>
+    <t>id_nompelu</t>
+  </si>
+  <si>
+    <t>Nompeluqueria</t>
+  </si>
+  <si>
+    <t>Cliente/servicio</t>
+  </si>
+  <si>
+    <t>Reserva/Cliente</t>
+  </si>
+  <si>
+    <t>Reserva/Peluqueria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,8 +594,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -526,6 +628,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -540,7 +648,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -569,6 +677,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -902,6 +1017,41 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{1A3D1899-E784-4CB7-85EA-F53F2C2A6698}">
+  <we:reference id="wa200004935" version="6.1.0.0" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200004935" version="6.1.0.0" store="wa200004935" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_FORMULABOT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_SENTIMENT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_INFO</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_FREEFORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_FORMULABOT_INFER</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7D3567-936D-4A60-8D0D-8C4475E3E630}">
   <dimension ref="A1:O11"/>
@@ -2164,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E5BC50-BC8A-4980-8D5E-0590C329F59C}">
-  <dimension ref="A3:W40"/>
+  <dimension ref="B3:V41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -2173,16 +2323,21 @@
     <col min="12" max="12" width="15.28515625" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C3" s="8" t="s">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
         <v>108</v>
       </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>103</v>
       </c>
@@ -2196,7 +2351,10 @@
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
     </row>
-    <row r="5" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
       <c r="C5" s="4" t="s">
         <v>105</v>
       </c>
@@ -2224,7 +2382,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>149</v>
+      </c>
       <c r="C6" s="4" t="s">
         <v>106</v>
       </c>
@@ -2256,7 +2417,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
       <c r="C7" s="4" t="s">
         <v>107</v>
       </c>
@@ -2288,13 +2452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="3:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="C8" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>78</v>
-      </c>
+    <row r="8" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
         <v>117</v>
       </c>
@@ -2320,22 +2478,19 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="3:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="C9" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="5">
-        <v>46275.708333333336</v>
+    <row r="9" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="G9" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>36</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I9" s="4"/>
       <c r="K9" t="s">
         <v>113</v>
       </c>
@@ -2355,12 +2510,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="3:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="C10" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>76</v>
+    <row r="10" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>112</v>
@@ -2375,12 +2533,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>111</v>
@@ -2395,17 +2556,22 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
       <c r="C12" s="4" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>120</v>
       </c>
       <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4" t="s">
@@ -2422,12 +2588,15 @@
       </c>
       <c r="T12" s="4"/>
     </row>
-    <row r="13" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>164</v>
+      </c>
       <c r="C13" s="4" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
         <v>121</v>
@@ -2457,9 +2626,12 @@
       </c>
       <c r="T13" s="4"/>
     </row>
-    <row r="14" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>165</v>
+      </c>
       <c r="C14" s="4" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>74</v>
@@ -2492,7 +2664,16 @@
       </c>
       <c r="T14" s="4"/>
     </row>
-    <row r="15" spans="3:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="H15" t="s">
         <v>123</v>
       </c>
@@ -2521,7 +2702,16 @@
       </c>
       <c r="T15" s="4"/>
     </row>
-    <row r="16" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H16" t="s">
         <v>124</v>
       </c>
@@ -2542,7 +2732,7 @@
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
         <v>125</v>
       </c>
@@ -2563,7 +2753,7 @@
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>126</v>
       </c>
@@ -2584,7 +2774,11 @@
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
     </row>
-    <row r="19" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" s="8"/>
       <c r="H19" t="s">
         <v>127</v>
       </c>
@@ -2597,583 +2791,2175 @@
       <c r="K19" t="s">
         <v>137</v>
       </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
+      <c r="M19" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" t="s">
+        <v>159</v>
+      </c>
       <c r="M20" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="N20" s="4"/>
+      <c r="N20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="O20" t="s">
+        <v>147</v>
+      </c>
       <c r="P20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R20" s="1"/>
+      <c r="R20" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="V20" s="1"/>
-      <c r="W20" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
       <c r="M21" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="N21" s="4"/>
+      <c r="N21" t="s">
+        <v>116</v>
+      </c>
+      <c r="O21" t="s">
+        <v>148</v>
+      </c>
       <c r="P21" s="5">
         <v>46273.333333333336</v>
       </c>
       <c r="Q21" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="R21" s="4"/>
-      <c r="S21" s="2"/>
+      <c r="R21" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="T21" s="2"/>
-      <c r="U21" s="2">
-        <v>55000</v>
-      </c>
       <c r="V21" s="4"/>
-      <c r="W21" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
       <c r="M22" s="4" t="s">
         <v>128</v>
       </c>
+      <c r="N22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O22" t="s">
+        <v>148</v>
+      </c>
       <c r="P22" s="5">
         <v>46273.333333333336</v>
       </c>
       <c r="Q22" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
+      <c r="R22" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="T22" s="2"/>
-      <c r="U22" s="2">
-        <v>53000</v>
-      </c>
       <c r="V22" s="4"/>
-      <c r="W22" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>84</v>
-      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="M23" t="s">
         <v>138</v>
       </c>
+      <c r="N23" t="s">
+        <v>117</v>
+      </c>
+      <c r="O23" t="s">
+        <v>149</v>
+      </c>
       <c r="P23" s="5">
         <v>46273.375</v>
       </c>
       <c r="Q23" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="R23" s="4"/>
-      <c r="S23" s="2"/>
+      <c r="R23" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="T23" s="2"/>
-      <c r="U23" s="2">
-        <v>88000</v>
-      </c>
       <c r="V23" s="4"/>
-      <c r="W23" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3104567891</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="4">
-        <v>1001234567</v>
-      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="M24" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="N24" t="s">
+        <v>117</v>
+      </c>
+      <c r="O24" t="s">
+        <v>149</v>
+      </c>
       <c r="P24" s="5">
         <v>46273.375</v>
       </c>
       <c r="Q24" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="R24" s="4"/>
-      <c r="S24" s="2"/>
+      <c r="R24" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="T24" s="2"/>
-      <c r="U24" s="2">
-        <v>105000</v>
-      </c>
       <c r="V24" s="4"/>
-      <c r="W24" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3115678902</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="4">
-        <v>1002345678</v>
-      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="M25" s="4" t="s">
         <v>129</v>
       </c>
+      <c r="N25" t="s">
+        <v>118</v>
+      </c>
+      <c r="O25" t="s">
+        <v>150</v>
+      </c>
       <c r="P25" s="5">
         <v>46273.416666666664</v>
       </c>
       <c r="Q25" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="R25" s="4"/>
-      <c r="S25" s="2"/>
+      <c r="R25" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="T25" s="2"/>
-      <c r="U25" s="2">
-        <v>95000</v>
-      </c>
       <c r="V25" s="4"/>
-      <c r="W25" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="4">
-        <v>3126789013</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="4">
-        <v>1003456789</v>
-      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="M26" s="4" t="s">
         <v>129</v>
       </c>
+      <c r="N26" t="s">
+        <v>118</v>
+      </c>
+      <c r="O26" t="s">
+        <v>150</v>
+      </c>
       <c r="P26" s="5">
         <v>46273.416666666664</v>
       </c>
       <c r="Q26" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="R26" s="4"/>
-      <c r="S26" s="2"/>
+      <c r="R26" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="T26" s="2"/>
-      <c r="U26" s="2">
-        <v>55000</v>
-      </c>
       <c r="V26" s="4"/>
-      <c r="W26" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="4">
-        <v>3104567891</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1001234567</v>
-      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
       <c r="M27" s="4" t="s">
         <v>130</v>
       </c>
+      <c r="N27" t="s">
+        <v>116</v>
+      </c>
+      <c r="O27" t="s">
+        <v>148</v>
+      </c>
       <c r="P27" s="5">
         <v>46274.458333333336</v>
       </c>
       <c r="Q27" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="R27" s="4"/>
-      <c r="S27" s="2"/>
+      <c r="R27" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="T27" s="2"/>
-      <c r="U27" s="2">
-        <v>58000</v>
-      </c>
       <c r="V27" s="4"/>
-      <c r="W27" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="4">
-        <v>3148901235</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="4">
-        <v>1005678901</v>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>130</v>
       </c>
+      <c r="N28" t="s">
+        <v>116</v>
+      </c>
+      <c r="O28" t="s">
+        <v>148</v>
+      </c>
       <c r="P28" s="5">
         <v>46274.458333333336</v>
       </c>
       <c r="Q28" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="R28" s="4"/>
-      <c r="S28" s="2"/>
+      <c r="R28" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="T28" s="2"/>
-      <c r="U28" s="2">
-        <v>75000</v>
-      </c>
       <c r="V28" s="4"/>
-      <c r="W28" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="4">
-        <v>3115678902</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="4">
-        <v>1002345678</v>
+    </row>
+    <row r="29" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3104567891</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1001234567</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>139</v>
       </c>
+      <c r="N29" t="s">
+        <v>153</v>
+      </c>
+      <c r="O29" t="s">
+        <v>149</v>
+      </c>
       <c r="P29" s="5">
         <v>46274.583333333336</v>
       </c>
       <c r="Q29" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="R29" s="4"/>
-      <c r="S29" s="2"/>
+      <c r="R29" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="T29" s="2"/>
-      <c r="U29" s="2">
-        <v>88000</v>
-      </c>
       <c r="V29" s="4"/>
-      <c r="W29" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="4">
-        <v>3160123457</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" s="4">
-        <v>1007890123</v>
+    </row>
+    <row r="30" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3115678902</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1002345678</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>139</v>
       </c>
+      <c r="N30" t="s">
+        <v>153</v>
+      </c>
+      <c r="O30" t="s">
+        <v>149</v>
+      </c>
       <c r="P30" s="5">
         <v>46274.583333333336</v>
       </c>
       <c r="Q30" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="R30" s="4"/>
-      <c r="S30" s="2"/>
+      <c r="R30" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="T30" s="2"/>
-      <c r="U30" s="2">
-        <v>75000</v>
-      </c>
       <c r="V30" s="4"/>
-      <c r="W30" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="4">
+    </row>
+    <row r="31" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="4">
         <v>3126789013</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="F31" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="4">
         <v>1003456789</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>140</v>
       </c>
+      <c r="N31" t="s">
+        <v>117</v>
+      </c>
+      <c r="O31" t="s">
+        <v>150</v>
+      </c>
       <c r="P31" s="5">
         <v>46274.625</v>
       </c>
       <c r="Q31" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="R31" s="4"/>
-    </row>
-    <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="4">
-        <v>3182345679</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1009012345</v>
+      <c r="R31" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="4">
+        <v>3104567891</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1001234567</v>
       </c>
       <c r="M32" t="s">
         <v>140</v>
       </c>
+      <c r="N32" t="s">
+        <v>117</v>
+      </c>
+      <c r="O32" t="s">
+        <v>150</v>
+      </c>
       <c r="P32" s="5">
         <v>46274.625</v>
       </c>
       <c r="Q32" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="R32" s="4"/>
-    </row>
-    <row r="33" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="4">
-        <v>3104567891</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="4">
-        <v>1001234567</v>
+      <c r="R32" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="4">
+        <v>3148901235</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="4">
+        <v>1005678901</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>141</v>
       </c>
+      <c r="N33" t="s">
+        <v>154</v>
+      </c>
+      <c r="O33" t="s">
+        <v>148</v>
+      </c>
       <c r="P33" s="5">
         <v>46275.666666666664</v>
       </c>
       <c r="Q33" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="R33" s="4"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R33" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="4">
+        <v>3115678902</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1002345678</v>
+      </c>
       <c r="M34" s="4" t="s">
         <v>141</v>
       </c>
+      <c r="N34" t="s">
+        <v>154</v>
+      </c>
+      <c r="O34" t="s">
+        <v>148</v>
+      </c>
       <c r="P34" s="5">
         <v>46275.666666666664</v>
       </c>
       <c r="Q34" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="R34" s="4"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R34" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3160123457</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1007890123</v>
+      </c>
       <c r="M35" s="4" t="s">
         <v>142</v>
       </c>
+      <c r="N35" t="s">
+        <v>118</v>
+      </c>
+      <c r="O35" t="s">
+        <v>149</v>
+      </c>
       <c r="P35" s="5">
         <v>46275.708333333336</v>
       </c>
       <c r="Q35" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="R35" s="4"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R35" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="4">
+        <v>3126789013</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1003456789</v>
+      </c>
       <c r="M36" s="4" t="s">
         <v>142</v>
       </c>
+      <c r="N36" t="s">
+        <v>118</v>
+      </c>
+      <c r="O36" t="s">
+        <v>149</v>
+      </c>
       <c r="P36" s="5">
         <v>46275.708333333336</v>
       </c>
       <c r="Q36" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="R36" s="4"/>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R36" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3182345679</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1009012345</v>
+      </c>
       <c r="M37" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="N37" t="s">
+        <v>155</v>
+      </c>
+      <c r="O37" t="s">
+        <v>149</v>
+      </c>
       <c r="P37" s="5">
         <v>46276.333333333336</v>
       </c>
       <c r="Q37" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="R37" s="4"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R37" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="3:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="4">
+        <v>3104567891</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1001234567</v>
+      </c>
       <c r="M38" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="N38" t="s">
+        <v>155</v>
+      </c>
+      <c r="O38" t="s">
+        <v>149</v>
+      </c>
       <c r="P38" s="5">
         <v>46276.333333333336</v>
       </c>
       <c r="Q38" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="R38" s="4"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R38" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
       <c r="M39" s="4" t="s">
         <v>144</v>
       </c>
+      <c r="N39" t="s">
+        <v>116</v>
+      </c>
+      <c r="O39" t="s">
+        <v>150</v>
+      </c>
       <c r="P39" s="5">
         <v>46276.375</v>
       </c>
       <c r="Q39" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="R39" s="4"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R39" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="3:19" x14ac:dyDescent="0.25">
       <c r="M40" s="5" t="s">
         <v>144</v>
       </c>
+      <c r="N40" t="s">
+        <v>116</v>
+      </c>
+      <c r="O40" t="s">
+        <v>150</v>
+      </c>
       <c r="P40" s="4" t="s">
         <v>12</v>
       </c>
       <c r="Q40" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="R40" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S41" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C3:D3"/>
+  <mergeCells count="9">
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="M19:R19"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="P4:S4"/>
-    <mergeCell ref="H12:I12"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D24" r:id="rId1" display="mailto:valentina@gmail.com" xr:uid="{7B712819-29A0-4A56-9D2E-5C14D46ACA36}"/>
-    <hyperlink ref="D25" r:id="rId2" display="mailto:mariana@gmail.com" xr:uid="{E8E89B70-30AC-4657-B82C-1AA7C54B57E5}"/>
-    <hyperlink ref="D26" r:id="rId3" display="mailto:sofia@gmail.com" xr:uid="{6F6C986D-6D4E-4233-BD80-45A27272DB2E}"/>
-    <hyperlink ref="D27" r:id="rId4" display="mailto:valentina@gmail.com" xr:uid="{ED703C51-2A3D-4B49-B7C4-BEF4AD91E129}"/>
-    <hyperlink ref="D28" r:id="rId5" display="mailto:gabriela@gmail.com" xr:uid="{D687AF52-7C42-4243-BD7D-1A15AE2F6352}"/>
-    <hyperlink ref="D29" r:id="rId6" display="mailto:mariana@gmail.com" xr:uid="{5334FF91-1058-4F6C-ABDA-E05930C259D7}"/>
-    <hyperlink ref="D30" r:id="rId7" display="mailto:natalia@gmail.com" xr:uid="{E62C7220-664F-49A8-851B-E74FC5EF72E3}"/>
-    <hyperlink ref="D31" r:id="rId8" display="mailto:sofia@gmail.com" xr:uid="{CBC30520-C90C-4527-8C2A-DE92CD7FBA0F}"/>
-    <hyperlink ref="D32" r:id="rId9" display="mailto:juliana@gmail.com" xr:uid="{59952E0F-6DF7-4E42-80F2-AF27CFDF7425}"/>
-    <hyperlink ref="D33" r:id="rId10" display="mailto:valentina@gmail.com" xr:uid="{BB4E77F7-C629-4026-B387-44CC7F059F1F}"/>
+    <hyperlink ref="E29" r:id="rId1" display="mailto:valentina@gmail.com" xr:uid="{7B712819-29A0-4A56-9D2E-5C14D46ACA36}"/>
+    <hyperlink ref="E30" r:id="rId2" display="mailto:mariana@gmail.com" xr:uid="{E8E89B70-30AC-4657-B82C-1AA7C54B57E5}"/>
+    <hyperlink ref="E31" r:id="rId3" display="mailto:sofia@gmail.com" xr:uid="{6F6C986D-6D4E-4233-BD80-45A27272DB2E}"/>
+    <hyperlink ref="E32" r:id="rId4" display="mailto:valentina@gmail.com" xr:uid="{ED703C51-2A3D-4B49-B7C4-BEF4AD91E129}"/>
+    <hyperlink ref="E33" r:id="rId5" display="mailto:gabriela@gmail.com" xr:uid="{D687AF52-7C42-4243-BD7D-1A15AE2F6352}"/>
+    <hyperlink ref="E34" r:id="rId6" display="mailto:mariana@gmail.com" xr:uid="{5334FF91-1058-4F6C-ABDA-E05930C259D7}"/>
+    <hyperlink ref="E35" r:id="rId7" display="mailto:natalia@gmail.com" xr:uid="{E62C7220-664F-49A8-851B-E74FC5EF72E3}"/>
+    <hyperlink ref="E36" r:id="rId8" display="mailto:sofia@gmail.com" xr:uid="{CBC30520-C90C-4527-8C2A-DE92CD7FBA0F}"/>
+    <hyperlink ref="E37" r:id="rId9" display="mailto:juliana@gmail.com" xr:uid="{59952E0F-6DF7-4E42-80F2-AF27CFDF7425}"/>
+    <hyperlink ref="E38" r:id="rId10" display="mailto:valentina@gmail.com" xr:uid="{BB4E77F7-C629-4026-B387-44CC7F059F1F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E8F2EB-3314-4D5D-9EEB-0C278F6CE5F7}">
+  <dimension ref="A2:V56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K2" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="K3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+    </row>
+    <row r="5" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="J8" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="P8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="F9" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="I9" s="4"/>
+      <c r="J9" t="s">
+        <v>121</v>
+      </c>
+      <c r="K9" t="s">
+        <v>120</v>
+      </c>
+      <c r="L9" t="s">
+        <v>132</v>
+      </c>
+      <c r="M9" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L10" s="2">
+        <v>30000</v>
+      </c>
+      <c r="M10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="2">
+        <v>25000</v>
+      </c>
+      <c r="M11" t="s">
+        <v>135</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="2">
+        <v>28000</v>
+      </c>
+      <c r="M12" t="s">
+        <v>134</v>
+      </c>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="2">
+        <v>60000</v>
+      </c>
+      <c r="M13" t="s">
+        <v>136</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="2">
+        <v>45000</v>
+      </c>
+      <c r="M14" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="2">
+        <v>50000</v>
+      </c>
+      <c r="M15" t="s">
+        <v>137</v>
+      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+    </row>
+    <row r="20" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3104567891</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1001234567</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="M20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="O20" t="s">
+        <v>147</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="4">
+        <v>3115678902</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1002345678</v>
+      </c>
+      <c r="H21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I21" t="s">
+        <v>122</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="N21" t="s">
+        <v>162</v>
+      </c>
+      <c r="O21" t="s">
+        <v>148</v>
+      </c>
+      <c r="P21" s="5">
+        <v>46273.333333333336</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="V21" s="4"/>
+    </row>
+    <row r="22" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="4">
+        <v>3126789013</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1003456789</v>
+      </c>
+      <c r="H22" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" t="s">
+        <v>123</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="N22" t="s">
+        <v>162</v>
+      </c>
+      <c r="O22" t="s">
+        <v>148</v>
+      </c>
+      <c r="P22" s="5">
+        <v>46273.333333333336</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="4">
+        <v>3104567891</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1001234567</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" t="s">
+        <v>125</v>
+      </c>
+      <c r="M23" t="s">
+        <v>138</v>
+      </c>
+      <c r="N23" t="s">
+        <v>163</v>
+      </c>
+      <c r="O23" t="s">
+        <v>149</v>
+      </c>
+      <c r="P23" s="5">
+        <v>46273.375</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T23" s="2"/>
+      <c r="V23" s="4"/>
+    </row>
+    <row r="24" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="4">
+        <v>3148901235</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1005678901</v>
+      </c>
+      <c r="H24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s">
+        <v>126</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="N24" t="s">
+        <v>163</v>
+      </c>
+      <c r="O24" t="s">
+        <v>149</v>
+      </c>
+      <c r="P24" s="5">
+        <v>46273.375</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="2"/>
+      <c r="V24" s="4"/>
+    </row>
+    <row r="25" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="4">
+        <v>3115678902</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1002345678</v>
+      </c>
+      <c r="H25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" t="s">
+        <v>122</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="N25" t="s">
+        <v>164</v>
+      </c>
+      <c r="O25" t="s">
+        <v>150</v>
+      </c>
+      <c r="P25" s="5">
+        <v>46273.416666666664</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T25" s="2"/>
+      <c r="V25" s="4"/>
+    </row>
+    <row r="26" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="4">
+        <v>3160123457</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1007890123</v>
+      </c>
+      <c r="H26" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" t="s">
+        <v>126</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="N26" t="s">
+        <v>164</v>
+      </c>
+      <c r="O26" t="s">
+        <v>150</v>
+      </c>
+      <c r="P26" s="5">
+        <v>46273.416666666664</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T26" s="2"/>
+      <c r="V26" s="4"/>
+    </row>
+    <row r="27" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="4">
+        <v>3126789013</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1003456789</v>
+      </c>
+      <c r="H27" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" t="s">
+        <v>123</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="N27" t="s">
+        <v>162</v>
+      </c>
+      <c r="O27" t="s">
+        <v>148</v>
+      </c>
+      <c r="P27" s="5">
+        <v>46274.458333333336</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T27" s="2"/>
+      <c r="V27" s="4"/>
+    </row>
+    <row r="28" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="4">
+        <v>3182345679</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="4">
+        <v>1009012345</v>
+      </c>
+      <c r="H28" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" t="s">
+        <v>124</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="N28" t="s">
+        <v>162</v>
+      </c>
+      <c r="O28" t="s">
+        <v>148</v>
+      </c>
+      <c r="P28" s="5">
+        <v>46274.458333333336</v>
+      </c>
+      <c r="Q28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T28" s="2"/>
+      <c r="V28" s="4"/>
+    </row>
+    <row r="29" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="4">
+        <v>3104567891</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1001234567</v>
+      </c>
+      <c r="H29" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" t="s">
+        <v>122</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="N29" t="s">
+        <v>165</v>
+      </c>
+      <c r="O29" t="s">
+        <v>149</v>
+      </c>
+      <c r="P29" s="5">
+        <v>46274.583333333336</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T29" s="2"/>
+      <c r="V29" s="4"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="H30" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="N30" t="s">
+        <v>165</v>
+      </c>
+      <c r="O30" t="s">
+        <v>149</v>
+      </c>
+      <c r="P30" s="5">
+        <v>46274.583333333336</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T30" s="2"/>
+      <c r="V30" s="4"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="H31" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" t="s">
+        <v>124</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="N31" t="s">
+        <v>163</v>
+      </c>
+      <c r="O31" t="s">
+        <v>150</v>
+      </c>
+      <c r="P31" s="5">
+        <v>46274.625</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="H32" t="s">
+        <v>118</v>
+      </c>
+      <c r="I32" t="s">
+        <v>125</v>
+      </c>
+      <c r="M32" t="s">
+        <v>140</v>
+      </c>
+      <c r="N32" t="s">
+        <v>163</v>
+      </c>
+      <c r="O32" t="s">
+        <v>150</v>
+      </c>
+      <c r="P32" s="5">
+        <v>46274.625</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R32" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H33" t="s">
+        <v>118</v>
+      </c>
+      <c r="I33" t="s">
+        <v>123</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="N33" t="s">
+        <v>166</v>
+      </c>
+      <c r="O33" t="s">
+        <v>148</v>
+      </c>
+      <c r="P33" s="5">
+        <v>46275.666666666664</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R33" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H34" t="s">
+        <v>118</v>
+      </c>
+      <c r="I34" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="N34" t="s">
+        <v>166</v>
+      </c>
+      <c r="O34" t="s">
+        <v>148</v>
+      </c>
+      <c r="P34" s="5">
+        <v>46275.666666666664</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H35" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35" t="s">
+        <v>126</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="N35" t="s">
+        <v>164</v>
+      </c>
+      <c r="O35" t="s">
+        <v>149</v>
+      </c>
+      <c r="P35" s="5">
+        <v>46275.708333333336</v>
+      </c>
+      <c r="Q35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>153</v>
+      </c>
+      <c r="I36" t="s">
+        <v>127</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="N36" t="s">
+        <v>164</v>
+      </c>
+      <c r="O36" t="s">
+        <v>149</v>
+      </c>
+      <c r="P36" s="5">
+        <v>46275.708333333336</v>
+      </c>
+      <c r="Q36" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H37" t="s">
+        <v>154</v>
+      </c>
+      <c r="I37" t="s">
+        <v>122</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="N37" t="s">
+        <v>167</v>
+      </c>
+      <c r="O37" t="s">
+        <v>149</v>
+      </c>
+      <c r="P37" s="5">
+        <v>46276.333333333336</v>
+      </c>
+      <c r="Q37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I38" t="s">
+        <v>124</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="N38" t="s">
+        <v>167</v>
+      </c>
+      <c r="O38" t="s">
+        <v>149</v>
+      </c>
+      <c r="P38" s="5">
+        <v>46276.333333333336</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="R38" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H39" t="s">
+        <v>155</v>
+      </c>
+      <c r="I39" t="s">
+        <v>124</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="N39" t="s">
+        <v>162</v>
+      </c>
+      <c r="O39" t="s">
+        <v>150</v>
+      </c>
+      <c r="P39" s="5">
+        <v>46276.375</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R39" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="H40" t="s">
+        <v>155</v>
+      </c>
+      <c r="I40" t="s">
+        <v>125</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="N40" t="s">
+        <v>162</v>
+      </c>
+      <c r="O40" t="s">
+        <v>150</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="R40" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S41" s="4"/>
+    </row>
+    <row r="46" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C46" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="G46" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="L46" s="12"/>
+    </row>
+    <row r="47" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" t="s">
+        <v>148</v>
+      </c>
+      <c r="H47" t="s">
+        <v>128</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J47" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>138</v>
+      </c>
+      <c r="D48" t="s">
+        <v>163</v>
+      </c>
+      <c r="E48" t="s">
+        <v>149</v>
+      </c>
+      <c r="H48" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J48" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49" t="s">
+        <v>150</v>
+      </c>
+      <c r="H49" t="s">
+        <v>129</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J49" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" t="s">
+        <v>148</v>
+      </c>
+      <c r="H50" t="s">
+        <v>130</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J50" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" t="s">
+        <v>165</v>
+      </c>
+      <c r="E51" t="s">
+        <v>149</v>
+      </c>
+      <c r="H51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" t="s">
+        <v>163</v>
+      </c>
+      <c r="E52" t="s">
+        <v>150</v>
+      </c>
+      <c r="H52" t="s">
+        <v>140</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J52" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" t="s">
+        <v>148</v>
+      </c>
+      <c r="H53" t="s">
+        <v>141</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" t="s">
+        <v>164</v>
+      </c>
+      <c r="E54" t="s">
+        <v>149</v>
+      </c>
+      <c r="H54" t="s">
+        <v>142</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J54" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" t="s">
+        <v>149</v>
+      </c>
+      <c r="H55" t="s">
+        <v>143</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J55" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>144</v>
+      </c>
+      <c r="D56" t="s">
+        <v>167</v>
+      </c>
+      <c r="E56" t="s">
+        <v>150</v>
+      </c>
+      <c r="H56" t="s">
+        <v>144</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="M19:R19"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="P4:S4"/>
+    <mergeCell ref="B9:D9"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C20" r:id="rId1" display="mailto:valentina@gmail.com" xr:uid="{66809A88-F1B9-4B56-B99F-AD2A3270599A}"/>
+    <hyperlink ref="C21" r:id="rId2" display="mailto:mariana@gmail.com" xr:uid="{6C51EF7C-9E85-40C6-95F8-4742F5AF1559}"/>
+    <hyperlink ref="C22" r:id="rId3" display="mailto:sofia@gmail.com" xr:uid="{DD91B802-942F-4300-9567-BA19E0782AB2}"/>
+    <hyperlink ref="C23" r:id="rId4" display="mailto:valentina@gmail.com" xr:uid="{3569BF7D-447B-481A-8A4C-73C61C0F52A6}"/>
+    <hyperlink ref="C24" r:id="rId5" display="mailto:gabriela@gmail.com" xr:uid="{9E3BD355-560D-4430-9512-74DAEBBB224E}"/>
+    <hyperlink ref="C25" r:id="rId6" display="mailto:mariana@gmail.com" xr:uid="{FC628FAD-C312-4217-9A7F-9EBE6F2DE8C6}"/>
+    <hyperlink ref="C26" r:id="rId7" display="mailto:natalia@gmail.com" xr:uid="{F67AE009-7A29-46F3-B073-58561D7C027B}"/>
+    <hyperlink ref="C27" r:id="rId8" display="mailto:sofia@gmail.com" xr:uid="{7154728C-5CEA-4B51-BBB2-A5A5D1E2BF0A}"/>
+    <hyperlink ref="C28" r:id="rId9" display="mailto:juliana@gmail.com" xr:uid="{3E62A596-345E-4FB4-BF0E-B2C679D941D6}"/>
+    <hyperlink ref="C29" r:id="rId10" display="mailto:valentina@gmail.com" xr:uid="{B4D3189E-E75C-4FDD-8DB5-3B419173E577}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\Glow_pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F312E958-D280-466C-8E7E-B0E17B9F0A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A3B056-111A-4819-9725-E4987DA7359C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{42CED176-6331-4827-B98C-A46AFC054923}"/>
   </bookViews>
@@ -732,15 +732,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -754,11 +748,13 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -772,11 +768,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2925,14 +2925,14 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
       <c r="P4" s="17" t="s">
         <v>117</v>
       </c>
@@ -2941,558 +2941,558 @@
       <c r="S4" s="17"/>
     </row>
     <row r="5" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="H5" s="9" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="H5" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <v>46273.333333333336</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="P6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>3104567891</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>1001234567</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="12">
         <v>46273.333333333336</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="P7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="Q7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R7" s="9" t="s">
+      <c r="R7" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="S7" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>3115678902</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>1002345678</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="12">
         <v>46273.375</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="R8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="S8" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>3126789013</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>1003456789</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="12">
         <v>46273.375</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="P9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="Q9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="R9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="S9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>3104567891</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>1001234567</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="12">
         <v>46273.416666666664</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="R10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>3148901235</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>1005678901</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="12">
         <v>46273.416666666664</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="P11" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="R11" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="S11" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>3115678902</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>1002345678</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="12">
         <v>46274.458333333336</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R12" s="9" t="s">
+      <c r="R12" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="S12" s="8" t="s">
         <v>41</v>
       </c>
       <c r="T12" s="4"/>
     </row>
     <row r="13" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>3160123457</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>1007890123</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <v>46274.458333333336</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
-      <c r="P13" s="9" t="s">
+      <c r="P13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R13" s="9" t="s">
+      <c r="R13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="8" t="s">
         <v>28</v>
       </c>
       <c r="T13" s="4"/>
     </row>
     <row r="14" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>3126789013</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>1003456789</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="12">
         <v>46274.583333333336</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="8" t="s">
         <v>23</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="9" t="s">
+      <c r="P14" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="Q14" s="9" t="s">
+      <c r="Q14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R14" s="9" t="s">
+      <c r="R14" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="S14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="T14" s="4"/>
     </row>
     <row r="15" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>3182345679</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>1009012345</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="12">
         <v>46274.583333333336</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="8" t="s">
         <v>23</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="9" t="s">
+      <c r="P15" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q15" s="9" t="s">
+      <c r="Q15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R15" s="9" t="s">
+      <c r="R15" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S15" s="9" t="s">
+      <c r="S15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="T15" s="4"/>
     </row>
     <row r="16" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>3104567891</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>1001234567</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="12">
         <v>46274.625</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="M16" s="8" t="s">
         <v>17</v>
       </c>
       <c r="N16" s="4"/>
@@ -3504,22 +3504,22 @@
       <c r="T16" s="4"/>
     </row>
     <row r="17" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="12">
         <v>46274.625</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="M17" s="8" t="s">
         <v>17</v>
       </c>
       <c r="N17" s="4"/>
@@ -3531,22 +3531,22 @@
       <c r="T17" s="4"/>
     </row>
     <row r="18" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="12">
         <v>46275.666666666664</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M18" s="8" t="s">
         <v>17</v>
       </c>
       <c r="N18" s="4"/>
@@ -3558,44 +3558,44 @@
       <c r="T18" s="4"/>
     </row>
     <row r="19" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="12">
         <v>46275.666666666664</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="M19" s="9" t="s">
+      <c r="M19" s="8" t="s">
         <v>17</v>
       </c>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="12">
         <v>46275.708333333336</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="M20" s="9" t="s">
+      <c r="M20" s="8" t="s">
         <v>23</v>
       </c>
       <c r="S20" s="3"/>
@@ -3603,426 +3603,426 @@
       <c r="V20" s="1"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="12">
         <v>46275.708333333336</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="M21" s="8" t="s">
         <v>23</v>
       </c>
       <c r="T21" s="2"/>
       <c r="V21" s="4"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="12">
         <v>46276.333333333336</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M22" s="8" t="s">
         <v>17</v>
       </c>
       <c r="T22" s="2"/>
     </row>
     <row r="23" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="12">
         <v>46276.333333333336</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M23" s="8" t="s">
         <v>17</v>
       </c>
       <c r="T23" s="2"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="12">
         <v>46276.375</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="L24" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="M24" s="9" t="s">
+      <c r="M24" s="8" t="s">
         <v>23</v>
       </c>
       <c r="T24" s="2"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="M25" s="8" t="s">
         <v>23</v>
       </c>
       <c r="T25" s="2"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
       <c r="T26" s="2"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="J27" s="10" t="s">
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="J27" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="K27" s="10"/>
-      <c r="M27" s="10" t="s">
+      <c r="K27" s="23"/>
+      <c r="M27" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="N27" s="10"/>
+      <c r="N27" s="23"/>
       <c r="T27" s="2"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="K28" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="M28" s="13" t="s">
+      <c r="M28" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="N28" s="7" t="s">
         <v>4</v>
       </c>
       <c r="T28" s="2"/>
       <c r="AC28" s="4"/>
     </row>
     <row r="29" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="K29" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M29" s="8" t="s">
+      <c r="M29" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="N29" s="8" t="s">
         <v>14</v>
       </c>
       <c r="T29" s="2"/>
     </row>
     <row r="30" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="K30" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="M30" s="8" t="s">
+      <c r="M30" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N30" s="9" t="s">
+      <c r="N30" s="8" t="s">
         <v>31</v>
       </c>
       <c r="T30" s="2"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M31" s="14" t="s">
+      <c r="M31" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="N31" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="M35" s="10" t="s">
+      <c r="M35" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
     </row>
     <row r="36" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="H36" s="10"/>
-      <c r="M36" s="8" t="s">
+      <c r="H36" s="23"/>
+      <c r="M36" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="N36" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="O36" s="8" t="s">
+      <c r="O36" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="P36" s="8" t="s">
+      <c r="P36" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="37" spans="6:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="M37" s="8" t="s">
+      <c r="M37" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="N37" s="9" t="s">
+      <c r="N37" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="O37" s="11">
+      <c r="O37" s="9">
         <v>30000</v>
       </c>
-      <c r="P37" s="8" t="s">
+      <c r="P37" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="38" spans="6:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="M38" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="N38" s="9" t="s">
+      <c r="N38" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="9">
         <v>25000</v>
       </c>
-      <c r="P38" s="8" t="s">
+      <c r="P38" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="39" spans="6:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M39" s="8" t="s">
+      <c r="M39" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="N39" s="9" t="s">
+      <c r="N39" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O39" s="11">
+      <c r="O39" s="9">
         <v>28000</v>
       </c>
-      <c r="P39" s="8" t="s">
+      <c r="P39" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="40" spans="6:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="M40" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="N40" s="9" t="s">
+      <c r="N40" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="O40" s="11">
+      <c r="O40" s="9">
         <v>60000</v>
       </c>
-      <c r="P40" s="8" t="s">
+      <c r="P40" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="41" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="M41" s="8" t="s">
+      <c r="M41" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="N41" s="9" t="s">
+      <c r="N41" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O41" s="11">
+      <c r="O41" s="9">
         <v>45000</v>
       </c>
-      <c r="P41" s="8" t="s">
+      <c r="P41" s="7" t="s">
         <v>134</v>
       </c>
       <c r="S41" s="4"/>
     </row>
     <row r="42" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="M42" s="8" t="s">
+      <c r="M42" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="N42" s="9" t="s">
+      <c r="N42" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="O42" s="11">
+      <c r="O42" s="9">
         <v>50000</v>
       </c>
-      <c r="P42" s="8" t="s">
+      <c r="P42" s="7" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4074,10 +4074,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="W1" s="15"/>
+      <c r="W1" s="21"/>
     </row>
     <row r="2" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
@@ -4088,83 +4088,83 @@
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
-      <c r="V2" s="8" t="s">
+      <c r="V2" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="3" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="V3" s="8" t="s">
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="V3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="W3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="Z3" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
     </row>
     <row r="4" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>46273.333333333336</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>82</v>
       </c>
       <c r="O4" s="17" t="s">
@@ -4174,214 +4174,214 @@
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="Z4" s="8" t="s">
+      <c r="Z4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="AA4" s="8" t="s">
+      <c r="AA4" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="AB4" s="8" t="s">
+      <c r="AB4" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="5" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>46273.333333333336</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>3104567891</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>1001234567</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="V5" s="8" t="s">
+      <c r="V5" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="W5" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Z5" s="8" t="s">
+      <c r="Z5" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="AA5" s="9" t="s">
+      <c r="AA5" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB5" s="8" t="s">
+      <c r="AB5" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="6" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>46273.375</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>3115678902</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="8">
         <v>1002345678</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="P6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="V6" s="8" t="s">
+      <c r="V6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="W6" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="Z6" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="AA6" s="9" t="s">
+      <c r="AA6" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AB6" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="7" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>46273.375</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>3126789013</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <v>1003456789</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="P7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="Q7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R7" s="9" t="s">
+      <c r="R7" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="S7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="V7" s="8" t="s">
+      <c r="V7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="W7" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="Z7" s="8" t="s">
+      <c r="Z7" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AA7" s="9" t="s">
+      <c r="AA7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB7" s="8" t="s">
+      <c r="AB7" s="7" t="s">
         <v>162</v>
       </c>
       <c r="AD7">
@@ -4389,526 +4389,526 @@
       </c>
     </row>
     <row r="8" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>46273.416666666664</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>3104567891</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <v>1001234567</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="R8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="S8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V8" s="8" t="s">
+      <c r="V8" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="W8" s="8" t="s">
+      <c r="W8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="Z8" s="8" t="s">
+      <c r="Z8" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="AA8" s="9" t="s">
+      <c r="AA8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB8" s="8" t="s">
+      <c r="AB8" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="9" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>46273.416666666664</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>3148901235</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <v>1005678901</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="P9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="Q9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="R9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="S9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="V9" s="8" t="s">
+      <c r="V9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="W9" s="8" t="s">
+      <c r="W9" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="Z9" s="8" t="s">
+      <c r="Z9" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AA9" s="9" t="s">
+      <c r="AA9" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="AB9" s="8" t="s">
+      <c r="AB9" s="7" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="10" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>46274.458333333336</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>3115678902</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="8">
         <v>1002345678</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="R10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V10" s="8" t="s">
+      <c r="V10" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="W10" s="8" t="s">
+      <c r="W10" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="Z10" s="8" t="s">
+      <c r="Z10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AA10" s="9" t="s">
+      <c r="AA10" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB10" s="8" t="s">
+      <c r="AB10" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="11" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>46274.458333333336</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>3160123457</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <v>1007890123</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="P11" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="R11" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="S11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="V11" s="8" t="s">
+      <c r="V11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="W11" s="8" t="s">
+      <c r="W11" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="Z11" s="8" t="s">
+      <c r="Z11" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="AA11" s="9" t="s">
+      <c r="AA11" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="AB11" s="8" t="s">
+      <c r="AB11" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="12" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>46274.583333333336</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>3126789013</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="8">
         <v>1003456789</v>
       </c>
       <c r="N12" s="4"/>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R12" s="9" t="s">
+      <c r="R12" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="S12" s="8" t="s">
         <v>41</v>
       </c>
       <c r="T12" s="4"/>
-      <c r="V12" s="8" t="s">
+      <c r="V12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="W12" s="8" t="s">
+      <c r="W12" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="Z12" s="8" t="s">
+      <c r="Z12" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AA12" s="9" t="s">
+      <c r="AA12" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB12" s="8" t="s">
+      <c r="AB12" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="13" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>46274.583333333336</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>3182345679</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <v>1009012345</v>
       </c>
       <c r="N13" s="4"/>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="P13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R13" s="9" t="s">
+      <c r="R13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="8" t="s">
         <v>28</v>
       </c>
       <c r="T13" s="4"/>
-      <c r="V13" s="8" t="s">
+      <c r="V13" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="W13" s="8" t="s">
+      <c r="W13" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="Z13" s="8" t="s">
+      <c r="Z13" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="AA13" s="9" t="s">
+      <c r="AA13" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="AB13" s="8" t="s">
+      <c r="AB13" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="14" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>46274.625</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>3104567891</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <v>1001234567</v>
       </c>
       <c r="N14" s="4"/>
-      <c r="O14" s="9" t="s">
+      <c r="O14" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="P14" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="Q14" s="9" t="s">
+      <c r="Q14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R14" s="9" t="s">
+      <c r="R14" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="S14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="T14" s="4"/>
-      <c r="V14" s="8" t="s">
+      <c r="V14" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="W14" s="8" t="s">
+      <c r="W14" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Z14" s="8" t="s">
+      <c r="Z14" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="AA14" s="9" t="s">
+      <c r="AA14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AB14" s="8" t="s">
+      <c r="AB14" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="15" spans="2:30" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>46274.625</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>176</v>
       </c>
       <c r="N15" s="4"/>
-      <c r="O15" s="9" t="s">
+      <c r="O15" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="P15" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="Q15" s="9" t="s">
+      <c r="Q15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="R15" s="9" t="s">
+      <c r="R15" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="S15" s="9" t="s">
+      <c r="S15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="T15" s="4"/>
-      <c r="V15" s="8" t="s">
+      <c r="V15" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="W15" s="8" t="s">
+      <c r="W15" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="16" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>46275.666666666664</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>176</v>
       </c>
       <c r="N16" s="4"/>
@@ -4918,37 +4918,37 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
-      <c r="V16" s="8" t="s">
+      <c r="V16" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="W16" s="8" t="s">
+      <c r="W16" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <v>46275.666666666664</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -4956,44 +4956,44 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
-      <c r="V17" s="8" t="s">
+      <c r="V17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="W17" s="8" t="s">
+      <c r="W17" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="Z17" s="15" t="s">
+      <c r="Z17" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="AA17" s="15"/>
-      <c r="AB17" s="15"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="21"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>46275.708333333336</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" s="7" t="s">
         <v>150</v>
       </c>
       <c r="N18" s="4"/>
@@ -5003,540 +5003,540 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="V18" s="8" t="s">
+      <c r="V18" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="W18" s="8" t="s">
+      <c r="W18" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="Z18" s="8" t="s">
+      <c r="Z18" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="AA18" s="8" t="s">
+      <c r="AA18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="AB18" s="8" t="s">
+      <c r="AB18" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>46275.708333333336</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N19" s="22" t="s">
+      <c r="N19" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="O19" s="22"/>
-      <c r="Q19" s="10" t="s">
+      <c r="O19" s="16"/>
+      <c r="Q19" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="23"/>
       <c r="S19" s="4"/>
-      <c r="V19" s="8" t="s">
+      <c r="V19" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="W19" s="8" t="s">
+      <c r="W19" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="Z19" s="8" t="s">
+      <c r="Z19" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="AA19" s="8" t="s">
+      <c r="AA19" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="AB19" s="8" t="s">
+      <c r="AB19" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>46276.333333333336</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="N20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="O20" s="8" t="s">
+      <c r="O20" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="Q20" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="R20" s="8" t="s">
+      <c r="R20" s="7" t="s">
         <v>157</v>
       </c>
       <c r="S20" s="3"/>
-      <c r="V20" s="8" t="s">
+      <c r="V20" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="W20" s="8" t="s">
+      <c r="W20" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="Z20" s="8" t="s">
+      <c r="Z20" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="AA20" s="8" t="s">
+      <c r="AA20" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="AB20" s="8" t="s">
+      <c r="AB20" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>46276.333333333336</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="N21" s="8" t="s">
+      <c r="N21" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="O21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="Q21" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="R21" s="8" t="s">
+      <c r="R21" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="V21" s="8" t="s">
+      <c r="V21" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="W21" s="8" t="s">
+      <c r="W21" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="Z21" s="8" t="s">
+      <c r="Z21" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AA21" s="8" t="s">
+      <c r="AA21" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="AB21" s="8" t="s">
+      <c r="AB21" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>46276.375</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="N22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="O22" s="11" t="s">
+      <c r="O22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q22" s="8" t="s">
+      <c r="Q22" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="R22" s="8" t="s">
+      <c r="R22" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="V22" s="8" t="s">
+      <c r="V22" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="W22" s="8" t="s">
+      <c r="W22" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Z22" s="8" t="s">
+      <c r="Z22" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="AA22" s="8" t="s">
+      <c r="AA22" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="AB22" s="8" t="s">
+      <c r="AB22" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="23" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Z23" s="8" t="s">
+      <c r="Z23" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AA23" s="8" t="s">
+      <c r="AA23" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="AB23" s="8" t="s">
+      <c r="AB23" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="24" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="L24" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Z24" s="8" t="s">
+      <c r="Z24" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AA24" s="8" t="s">
+      <c r="AA24" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="AB24" s="8" t="s">
+      <c r="AB24" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="25" spans="2:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Z25" s="8" t="s">
+      <c r="Z25" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="AA25" s="8" t="s">
+      <c r="AA25" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AB25" s="8" t="s">
+      <c r="AB25" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="26" spans="2:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="7"/>
+      <c r="D26" s="22"/>
       <c r="F26" s="18" t="s">
         <v>106</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="20"/>
-      <c r="J26" s="21" t="s">
+      <c r="J26" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="K26" s="21"/>
-      <c r="N26" s="10" t="s">
+      <c r="K26" s="14"/>
+      <c r="N26" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="Z26" s="8" t="s">
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="Z26" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AA26" s="8" t="s">
+      <c r="AA26" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="AB26" s="8" t="s">
+      <c r="AB26" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="2:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J27" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="K27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="N27" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="O27" s="8" t="s">
+      <c r="O27" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="P27" s="8" t="s">
+      <c r="P27" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="Q27" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="Z27" s="8" t="s">
+      <c r="Z27" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="AA27" s="8" t="s">
+      <c r="AA27" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AB27" s="8" t="s">
+      <c r="AB27" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="28" spans="2:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="N28" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="O28" s="9" t="s">
+      <c r="O28" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="P28" s="11">
+      <c r="P28" s="9">
         <v>30000</v>
       </c>
-      <c r="Q28" s="8" t="s">
+      <c r="Q28" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="Z28" s="8" t="s">
+      <c r="Z28" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="AA28" s="8" t="s">
+      <c r="AA28" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AB28" s="8" t="s">
+      <c r="AB28" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="29" spans="2:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="N29" s="8" t="s">
+      <c r="N29" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="O29" s="9" t="s">
+      <c r="O29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="P29" s="11">
+      <c r="P29" s="9">
         <v>25000</v>
       </c>
-      <c r="Q29" s="8" t="s">
+      <c r="Q29" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="30" spans="2:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="J30" s="14" t="s">
+      <c r="J30" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K30" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="N30" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="O30" s="9" t="s">
+      <c r="O30" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="P30" s="11">
+      <c r="P30" s="9">
         <v>28000</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="Q30" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="N31" s="8" t="s">
+      <c r="N31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="O31" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="P31" s="11">
+      <c r="P31" s="9">
         <v>60000</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="Q31" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="N32" s="8" t="s">
+      <c r="N32" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O32" s="9" t="s">
+      <c r="O32" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P32" s="11">
+      <c r="P32" s="9">
         <v>45000</v>
       </c>
-      <c r="Q32" s="8" t="s">
+      <c r="Q32" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="33" spans="14:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="N33" s="8" t="s">
+      <c r="N33" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="O33" s="9" t="s">
+      <c r="O33" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="P33" s="11">
+      <c r="P33" s="9">
         <v>50000</v>
       </c>
-      <c r="Q33" s="8" t="s">
+      <c r="Q33" s="7" t="s">
         <v>135</v>
       </c>
     </row>
@@ -5545,11 +5545,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="C26:D26"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="Z17:AB17"/>
     <mergeCell ref="B2:G2"/>
@@ -5557,6 +5552,11 @@
     <mergeCell ref="N26:Q26"/>
     <mergeCell ref="I3:M3"/>
     <mergeCell ref="J17:L17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="Z3:AB3"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
